--- a/upload/downloads.xlsx
+++ b/upload/downloads.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8813F02B-45F1-4671-A704-A5DB17021FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E75D87F-5F3C-4D66-BCF0-90408E7DCE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="15480" xr2:uid="{925A4E02-7B21-415A-B129-1D775413F843}"/>
+    <workbookView xWindow="3495" yWindow="795" windowWidth="15300" windowHeight="7785" xr2:uid="{925A4E02-7B21-415A-B129-1D775413F843}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$B$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>descricao</t>
   </si>
@@ -132,6 +135,42 @@
   </si>
   <si>
     <t>https://drive.google.com/drive/u/0/folders/1WK0ZWYalEfOJbdepesACwXs6fL6oxw6Y</t>
+  </si>
+  <si>
+    <t>Resumo de Conceitos</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1K4g8EXGjkVYJG8iQzenV-phLGCeRqpic</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1vhbLBUxZF-IQzQ1Z2C2Y4x_Sra2A3F_B</t>
+  </si>
+  <si>
+    <t>Treinamento SISOR</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1zp2DePNIvORNqSMs2FW8D-I3qpBcZrIN</t>
+  </si>
+  <si>
+    <t>Treinamento SIGPLAN</t>
+  </si>
+  <si>
+    <t>https://www.mg.gov.br/planejamento/pagina/planejamento-e-orcamento/plano-plurianual-de-acao-governamental-ppag/plano-plurianual-de-acao</t>
+  </si>
+  <si>
+    <t>Cronograma do Processo de Elaboração do PPAG 2024-2027 da LOA 2026</t>
+  </si>
+  <si>
+    <t>Manual de Bolso</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1KC4wimcA8unP1lsmUNmmdddNmPKz3v5t</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1f81_cGxX5IxYImXPAlMVx9SXITTru4JM</t>
+  </si>
+  <si>
+    <t>Manula de Elaboração e Revisão do PPAG 2024-2027 e LOA 2026</t>
   </si>
 </sst>
 </file>
@@ -503,8 +542,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C55ADC3B-7402-4DA9-96F5-39C8F5871021}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="90.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -516,125 +558,178 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B1" xr:uid="{C55ADC3B-7402-4DA9-96F5-39C8F5871021}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B22">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>